--- a/Ribaue_Perfil_Nao_Enco.xlsx
+++ b/Ribaue_Perfil_Nao_Enco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Abrindo_Oportunidades/2026/Dash_Abrindo_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_13D83CCD8F79A8D366075C52F37BD272EAC953E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CADACA4-2836-4731-9869-49219F17E706}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_46D3C77019C1D9A14B76907C7D4E2E1568628611" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD599E04-1689-43CD-9BAF-F432D1034278}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
   <si>
     <t>Data_Registo</t>
   </si>
@@ -85,22 +85,22 @@
     <t>09-Apr-2026 10:23:21</t>
   </si>
   <si>
-    <t>Adino João</t>
+    <t>Marlene João Alfredo</t>
   </si>
   <si>
     <t>Ribaue</t>
   </si>
   <si>
-    <t>Masculino</t>
-  </si>
-  <si>
-    <t>Turma 5</t>
-  </si>
-  <si>
-    <t>NACARROANE</t>
-  </si>
-  <si>
-    <t>RAIMUNDO JULIO AFONSO</t>
+    <t>Feminino</t>
+  </si>
+  <si>
+    <t>Turma 1</t>
+  </si>
+  <si>
+    <t>NAMALE</t>
+  </si>
+  <si>
+    <t>EULANIA MANUEL</t>
   </si>
   <si>
     <t>Presente</t>
@@ -109,100 +109,34 @@
     <t>Ausente</t>
   </si>
   <si>
+    <t>27-Apr-2026 11:57:52</t>
+  </si>
+  <si>
+    <t>Carla Alfredo Albino</t>
+  </si>
+  <si>
+    <t>Turma 2</t>
+  </si>
+  <si>
+    <t>MANICA</t>
+  </si>
+  <si>
+    <t>MARIANA FELIZARDO</t>
+  </si>
+  <si>
+    <t>27-Apr-2026 13:22:26</t>
+  </si>
+  <si>
     <t>Sérgio Rafael</t>
   </si>
   <si>
-    <t>Feminino</t>
-  </si>
-  <si>
     <t>Turma 6</t>
   </si>
   <si>
     <t>NAMUALI</t>
   </si>
   <si>
-    <t>TORICA SILVESTRE ANTONIO</t>
-  </si>
-  <si>
-    <t>27-Apr-2026 13:22:26</t>
-  </si>
-  <si>
     <t>ESTEFANIA FELIZARDO</t>
-  </si>
-  <si>
-    <t>Agostinho Júlio Adelino</t>
-  </si>
-  <si>
-    <t>Turma 4</t>
-  </si>
-  <si>
-    <t>ALFEU JULIO</t>
-  </si>
-  <si>
-    <t>27-Apr-2026 13:23:31</t>
-  </si>
-  <si>
-    <t>GUITERIA ALVES</t>
-  </si>
-  <si>
-    <t>Marlene João Alfredo</t>
-  </si>
-  <si>
-    <t>Turma 1</t>
-  </si>
-  <si>
-    <t>NAMALE</t>
-  </si>
-  <si>
-    <t>EULANIA MANUEL</t>
-  </si>
-  <si>
-    <t>27-Apr-2026 11:57:52</t>
-  </si>
-  <si>
-    <t>Carla Alfredo Albino</t>
-  </si>
-  <si>
-    <t>Turma 2</t>
-  </si>
-  <si>
-    <t>MANICA</t>
-  </si>
-  <si>
-    <t>MARIANA FELIZARDO</t>
-  </si>
-  <si>
-    <t>CURRAPE</t>
-  </si>
-  <si>
-    <t>ALBERTINA VENANCIO</t>
-  </si>
-  <si>
-    <t>DALILA CELESTINO</t>
-  </si>
-  <si>
-    <t>CACILDA MANUEL</t>
-  </si>
-  <si>
-    <t>IXILDO ALBERTO</t>
-  </si>
-  <si>
-    <t>27-Apr-2026 11:53:33</t>
-  </si>
-  <si>
-    <t>ENIA JAIME</t>
-  </si>
-  <si>
-    <t>27-Apr-2026 11:52:51</t>
-  </si>
-  <si>
-    <t>ATIJA  ANSELMO RUA</t>
-  </si>
-  <si>
-    <t>27-Apr-2026 11:53:59</t>
-  </si>
-  <si>
-    <t>TELMA JOSE LAMPIAO</t>
   </si>
 </sst>
 </file>
@@ -226,18 +160,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -252,12 +180,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,14 +489,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +560,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -657,29 +586,32 @@
         <v>27</v>
       </c>
       <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
         <v>27</v>
       </c>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
       <c r="R2" t="s">
         <v>27</v>
       </c>
@@ -687,21 +619,21 @@
         <v>27</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
@@ -712,67 +644,34 @@
       <c r="G3" t="s">
         <v>33</v>
       </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R3" t="s">
-        <v>28</v>
-      </c>
       <c r="S3" t="s">
         <v>28</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
         <v>27</v>
@@ -812,607 +711,6 @@
       </c>
       <c r="T4">
         <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>27</v>
-      </c>
-      <c r="R6" t="s">
-        <v>27</v>
-      </c>
-      <c r="S6" t="s">
-        <v>27</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" t="s">
-        <v>27</v>
-      </c>
-      <c r="S7" t="s">
-        <v>27</v>
-      </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" t="s">
-        <v>49</v>
-      </c>
-      <c r="S8" t="s">
-        <v>28</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" t="s">
-        <v>27</v>
-      </c>
-      <c r="P9" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>28</v>
-      </c>
-      <c r="R9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S9" t="s">
-        <v>28</v>
-      </c>
-      <c r="T9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" t="s">
-        <v>28</v>
-      </c>
-      <c r="S10" t="s">
-        <v>27</v>
-      </c>
-      <c r="T10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" t="s">
-        <v>27</v>
-      </c>
-      <c r="N11" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>27</v>
-      </c>
-      <c r="R11" t="s">
-        <v>28</v>
-      </c>
-      <c r="S11" t="s">
-        <v>27</v>
-      </c>
-      <c r="T11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>28</v>
-      </c>
-      <c r="R12" t="s">
-        <v>28</v>
-      </c>
-      <c r="S12" t="s">
-        <v>28</v>
-      </c>
-      <c r="T12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" t="s">
-        <v>56</v>
-      </c>
-      <c r="P13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" t="s">
-        <v>28</v>
-      </c>
-      <c r="S13" t="s">
-        <v>28</v>
-      </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>28</v>
-      </c>
-      <c r="R14" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" t="s">
-        <v>27</v>
-      </c>
-      <c r="T14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" t="s">
-        <v>60</v>
-      </c>
-      <c r="P15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>27</v>
-      </c>
-      <c r="R15" t="s">
-        <v>28</v>
-      </c>
-      <c r="S15" t="s">
-        <v>28</v>
-      </c>
-      <c r="T15">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1421,6 +719,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -1655,34 +973,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C79EAA23-3F7B-4A40-9920-7A15A09F4343}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F920C0F4-7E92-48CB-AFFF-D946F18A1C32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B693B697-42E1-4288-A776-982B8E5F7036}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E49F934D-34B1-4F2E-AC34-2314146ECD41}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9047D877-BEC8-4CE1-93D2-BA38B446139E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D099B70-5254-420A-835A-327366C4AF2B}"/>
 </file>